--- a/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
+++ b/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
@@ -8,8 +8,12 @@
   <sheets>
     <sheet name="Table 14.1.1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 14.1.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Listing 16.2.7.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Figure 14.3.1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 14.3.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Table 14.3.2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 14.2.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Listing 16.2.7.1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Listing 16.2.4.1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Figure 14.3.1" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -392,7 +396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Summary of Subject Disposition</t>
+          <t>Subject Disposition</t>
         </is>
       </c>
     </row>
@@ -838,6 +842,724 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table 14.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview of Treatment-Emergent Adverse Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t xml:space="preserve">Safety Population </t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t>(ADSL.SAFFL='Y')</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Category</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[columns -&gt; ADAE.TRT01A; source ADAE]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Any TEAE</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.TRTEMFL = 'Y']</t>
+          </r>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Serious TEAE</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.AESER = 'Y']</t>
+          </r>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>TEAE by severity, n (%)</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.ASEV; once/subject ADAE.AOCCIFL]</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Severe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A subject is counted once in each severity they report. Percentages are of the safety population.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table 14.3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treatment-Emergent Adverse Events by System Organ Class and Preferred Term</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t xml:space="preserve">Safety Population </t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t>(ADSL.SAFFL='Y')</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>System Organ Class / Preferred Term</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[columns -&gt; ADAE.TRT01A; source ADAE]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Subjects with any TEAE</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.TRTEMFL = 'Y']</t>
+          </r>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>&lt;System Organ Class&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.AESOC]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>&lt;Preferred Term&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADAE.AEDECOD]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A subject is counted once per system organ class and once per term.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table 14.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Study Drug Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t xml:space="preserve">Safety Population </t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t>(ADSL.SAFFL='Y')</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Statistic</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[columns -&gt; ADEX.TRT01A; source ADEX]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Duration of exposure (days)</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADEX.AVAL WHERE ADEX.PARAMCD='TDURD']</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Min, Max</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xx, xx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>xx, xx</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>xx, xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Average daily dose (mg)</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADEX.AVAL WHERE ADEX.PARAMCD='AVDDSE']</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>xx.x (xx.xx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Exposure is derived from ADEX; one record per subject per parameter.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1017,7 +1739,188 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Listing 16.2.4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Listing of Concomitant Medications</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t xml:space="preserve">Safety Population </t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t>(ADSL.SAFFL='Y')</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Subject</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADCM.USUBJID]  [row: ADCM.AOCCPFL='Y'; source ADCM]</t>
+          </r>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Treatment</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADCM.TRTA]</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Reported term</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADCM.CMTRT]</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>WHODrug PT</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADCM.CMDECOD]</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="10"/>
+              <color rgb="FF000000"/>
+            </rPr>
+            <t>Indication</t>
+          </r>
+          <r>
+            <rPr>
+              <i/>
+              <sz val="8"/>
+              <color rgb="FFC00000"/>
+            </rPr>
+            <t xml:space="preserve">
+[ADCM.CMINDC]</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xxx-xxxx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xxxx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>xxxx</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>xxxx</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xxxx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
+++ b/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
@@ -1230,7 +1230,7 @@
               <color rgb="FFC00000"/>
             </rPr>
             <t xml:space="preserve">
-[ADAE.AESOC]</t>
+[ADAE.AESOC WHERE ADAE.TRTEMFL='Y']</t>
           </r>
         </is>
       </c>
@@ -1267,7 +1267,7 @@
               <color rgb="FFC00000"/>
             </rPr>
             <t xml:space="preserve">
-[ADAE.AEDECOD]</t>
+[ADAE.AEDECOD WHERE ADAE.TRTEMFL='Y']</t>
           </r>
         </is>
       </c>

--- a/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
+++ b/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
@@ -897,7 +897,7 @@
               <color rgb="FFC00000"/>
             </rPr>
             <t xml:space="preserve">
-[columns -&gt; ADAE.TRT01A; source ADAE]</t>
+[columns -&gt; ADSL.TRT01A; source ADAE]</t>
           </r>
         </is>
       </c>
@@ -1156,7 +1156,7 @@
               <color rgb="FFC00000"/>
             </rPr>
             <t xml:space="preserve">
-[columns -&gt; ADAE.TRT01A; source ADAE]</t>
+[columns -&gt; ADSL.TRT01A; source ADAE]</t>
           </r>
         </is>
       </c>
@@ -1364,7 +1364,7 @@
               <color rgb="FFC00000"/>
             </rPr>
             <t xml:space="preserve">
-[columns -&gt; ADEX.TRT01A; source ADEX]</t>
+[columns -&gt; ADSL.TRT01A; source ADEX]</t>
           </r>
         </is>
       </c>

--- a/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
+++ b/inst/extdata/example_cdsc_alz_201/annotated_shell.xlsx
@@ -1101,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -1175,6 +1175,11 @@
           <t>Xanomeline High Dose</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1212,6 +1217,11 @@
           <t>xx (xx.x)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1249,6 +1259,11 @@
           <t>xx (xx.x)</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1286,6 +1301,11 @@
           <t>xx (xx.x)</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xx (xx.x)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1296,10 +1316,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
